--- a/data/tags/סינגלים חדשים/global/2026-04-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week05/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מיתריי – שיהא בי את האומץ</v>
+        <v>נטע ברזילי – אוקסיטוצין</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-29</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%aa%d7%a8%d7%99%d7%99-%d7%a9%d7%99%d7%94%d7%90-%d7%91%d7%99-%d7%90%d7%aa-%d7%94%d7%90%d7%95%d7%9e%d7%a5/</v>
+        <v>https://yosmusic.com/%d7%a0%d7%98%d7%a2-%d7%91%d7%a8%d7%96%d7%99%d7%9c%d7%99-%d7%90%d7%95%d7%a7%d7%a1%d7%99%d7%98%d7%95%d7%a6%d7%99%d7%9f/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-29</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"שיהא בי את האומץ” של מיתריי (מאיה ביתנר) הוא שיר שממוקם בין תפילה אישית לבין טקס קולקטיבי. זה לא רק שיר במובן הפופולרי אלא חוויה כמעט מדיטטיבית־שבטית, שמבקשת לפרק פחדים ולהזמין חופש. ליבת  השיר נמצאת במשפט החוזר: "שיהא בי את</v>
+        <v>"אוקסיטוצין" של נטע ברזילי (מתוך האלבום "סרנדה") מציג צד שקט, עדין ואינטימי יחסית למה שמזוהה איתה בדרך כלל. במקום אנרגיה מתפרצת והפקה אלקטרונית, יש כאן בלדה רכה עם נגיעות של בוסה נובה ועיבוד אקוסטי מינימליסטי – בחירה שמשרתת  את התוכן</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מיתריי – שיהא בי את האומץ</v>
+        <v>נטע ברזילי – אוקסיטוצין</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-04-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week05/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נטע ברזילי – אוקסיטוצין</v>
+        <v>רותם שפי – רילוקיישן</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-29</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%98%d7%a2-%d7%91%d7%a8%d7%96%d7%99%d7%9c%d7%99-%d7%90%d7%95%d7%a7%d7%a1%d7%99%d7%98%d7%95%d7%a6%d7%99%d7%9f/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%aa%d7%9d-%d7%a9%d7%a4%d7%99-%d7%a8%d7%99%d7%9c%d7%95%d7%a7%d7%99%d7%99%d7%a9%d7%9f/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-29</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"אוקסיטוצין" של נטע ברזילי (מתוך האלבום "סרנדה") מציג צד שקט, עדין ואינטימי יחסית למה שמזוהה איתה בדרך כלל. במקום אנרגיה מתפרצת והפקה אלקטרונית, יש כאן בלדה רכה עם נגיעות של בוסה נובה ועיבוד אקוסטי מינימליסטי – בחירה שמשרתת  את התוכן</v>
+        <v>"רילוקיישן" של רותם שפי הוא טקסט שנשען על קלילות לכאורה,  אבל מתחתיה מסתתרת אמירה חדה על חיים בתוך מציאות לא יציבה. הוא משלב ראפ עם R&amp;B גרובי והפקה אלקטרונית, שמייצרת תחושת זרימה כמעט “כיפית”, בניגוד מעניין לתוכן הכאוטי. בפתיחה יש</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נטע ברזילי – אוקסיטוצין</v>
+        <v>רותם שפי – רילוקיישן</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-04-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רותם שפי – רילוקיישן</v>
+        <v>פרחי ירושלים - האור שלא יכבה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-29</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%95%d7%aa%d7%9d-%d7%a9%d7%a4%d7%99-%d7%a8%d7%99%d7%9c%d7%95%d7%a7%d7%99%d7%99%d7%a9%d7%9f/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410653&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-29</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"רילוקיישן" של רותם שפי הוא טקסט שנשען על קלילות לכאורה,  אבל מתחתיה מסתתרת אמירה חדה על חיים בתוך מציאות לא יציבה. הוא משלב ראפ עם R&amp;B גרובי והפקה אלקטרונית, שמייצרת תחושת זרימה כמעט “כיפית”, בניגוד מעניין לתוכן הכאוטי. בפתיחה יש</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,316 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רותם שפי – רילוקיישן</v>
+        <v>פרחי ירושלים - האור שלא יכבה</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>אופיר חדד- ילדות העיר שלי</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410652&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>אופיר חדד- ילדות העיר שלי</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>שלומי ימין - רוצה להיות שלך</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410651&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>שלומי ימין - רוצה להיות שלך</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>שחר יעקב - פרחים מנייר - גרסת היוצר</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410650&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>שחר יעקב - פרחים מנייר - גרסת היוצר</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>רותם שפי - רילוקיישן</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410649&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>רותם שפי - רילוקיישן</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>פרידה - ילדה מבורכת</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410648&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>פרידה - ילדה מבורכת</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>נתי בן שלום - שוב יכול</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410647&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>נתי בן שלום - שוב יכול</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>ברק לוי - עוד לא ויתרתי עלינו</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410646&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>ברק לוי - עוד לא ויתרתי עלינו</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אלעד אביבי - ימנו זלקה</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410645&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אלעד אביבי - ימנו זלקה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>פרחי ירושלים - האור שלא יכבה</v>
+        <v>רוני בר הדס – אמא מלכה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410653&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a0%d7%99-%d7%91%d7%a8-%d7%94%d7%93%d7%a1-%d7%90%d7%9e%d7%90-%d7%9e%d7%9c%d7%9b%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>“אמא מלכה” של רוני בר הדס הוא פופ עכשווי שמצליח להיות גם קליט ושובב  וגם רגשי וכנה מתחת לפני השטח. יש כאן עטיפה מתקתקה, כמעט “מרקידה”, שבתוכה יושב טקסט חשוף על מועקה, בדידות ודימוי עצמי. “יש לי אלף ואחת סיבות</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,316 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>פרחי ירושלים - האור שלא יכבה</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>אופיר חדד- ילדות העיר שלי</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-04-29</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410652&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-04-29</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>אופיר חדד- ילדות העיר שלי</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>שלומי ימין - רוצה להיות שלך</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-04-29</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410651&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-04-29</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>שלומי ימין - רוצה להיות שלך</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>שחר יעקב - פרחים מנייר - גרסת היוצר</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-04-29</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410650&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-04-29</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>שחר יעקב - פרחים מנייר - גרסת היוצר</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>רותם שפי - רילוקיישן</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-04-29</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410649&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-04-29</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>רותם שפי - רילוקיישן</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>פרידה - ילדה מבורכת</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-04-29</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410648&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-04-29</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>פרידה - ילדה מבורכת</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>נתי בן שלום - שוב יכול</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-04-29</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410647&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-04-29</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>נתי בן שלום - שוב יכול</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>ברק לוי - עוד לא ויתרתי עלינו</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-04-29</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410646&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-04-29</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>ברק לוי - עוד לא ויתרתי עלינו</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>אלעד אביבי - ימנו זלקה</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-04-29</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410645&amp;sid=6c07fe98cc20b7aff661fe5c5a75e338</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-04-29</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>אלעד אביבי - ימנו זלקה</v>
+        <v>רוני בר הדס – אמא מלכה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>